--- a/data/raw/sheets/sucursales.xlsx
+++ b/data/raw/sheets/sucursales.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Veracruz 1</t>
+          <t>Sucursal Corporativo JUC Veracruz 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Ciudad de Mexico 2</t>
+          <t>Sucursal Corporativo JUC Ciudad de Mexico 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Guadalajara 3</t>
+          <t>Sucursal Corporativo JUC Guadalajara 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Monterrey 4</t>
+          <t>Sucursal Corporativo JUC Monterrey 4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Puebla 5</t>
+          <t>Sucursal Corporativo JUC Puebla 5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Queretaro 6</t>
+          <t>Sucursal Corporativo JUC Queretaro 6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Cancun 7</t>
+          <t>Sucursal Corporativo JUC Cancun 7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Merida 8</t>
+          <t>Sucursal Corporativo JUC Merida 8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Tijuana 9</t>
+          <t>Sucursal Corporativo JUC Tijuana 9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Leon 10</t>
+          <t>Sucursal Corporativo JUC Leon 10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Veracruz 11</t>
+          <t>Sucursal Corporativo JUC Veracruz 11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sucursal NovaCommerce Ciudad de Mexico 12</t>
+          <t>Sucursal Corporativo JUC Ciudad de Mexico 12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
